--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487652_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487652_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.8949</v>
+        <v>12.1011</v>
       </c>
       <c r="E2" t="n">
-        <v>12.102</v>
+        <v>12.3628</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2071</v>
+        <v>-0.2617</v>
       </c>
       <c r="G2" t="n">
         <v>9.647399999999999</v>
@@ -610,13 +610,13 @@
         <v>2.7164</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1227</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0617</v>
+        <v>0.3224</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1843</v>
+        <v>-0.2389</v>
       </c>
       <c r="V2" t="n">
         <v>1.788</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.7366</v>
+        <v>6.0608</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9812</v>
+        <v>2.1419</v>
       </c>
       <c r="F3" t="n">
-        <v>3.7554</v>
+        <v>3.9189</v>
       </c>
       <c r="G3" t="n">
         <v>5.2217</v>
@@ -688,13 +688,13 @@
         <v>2.1344</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5224</v>
+        <v>-0.1982</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1828</v>
+        <v>0.3435</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7052</v>
+        <v>-0.5417</v>
       </c>
       <c r="V3" t="n">
         <v>1.0373</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.9441</v>
+        <v>4.6075</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0041</v>
+        <v>1.8855</v>
       </c>
       <c r="F4" t="n">
-        <v>2.94</v>
+        <v>2.722</v>
       </c>
       <c r="G4" t="n">
         <v>2.7973</v>
@@ -766,13 +766,13 @@
         <v>3.4926</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5592</v>
+        <v>-0.8958</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1233</v>
+        <v>0.0047</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6825</v>
+        <v>-0.9006</v>
       </c>
       <c r="V4" t="n">
         <v>0.3776</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.6364</v>
+        <v>3.7655</v>
       </c>
       <c r="E5" t="n">
-        <v>4.7607</v>
+        <v>3.7807</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1242</v>
+        <v>-0.0152</v>
       </c>
       <c r="G5" t="n">
         <v>3.5207</v>
@@ -844,13 +844,13 @@
         <v>2.3284</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2425</v>
+        <v>-1.1134</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0935</v>
+        <v>0.1135</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.336</v>
+        <v>-1.227</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. ALONSO GONZÁLEZ</t>
+          <t>P. FUENTE DIEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3401</v>
+        <v>-0.0458</v>
       </c>
       <c r="E6" t="n">
-        <v>0.103</v>
+        <v>1.162</v>
       </c>
       <c r="F6" t="n">
-        <v>0.237</v>
+        <v>-1.2078</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6543</v>
+        <v>3.3248</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3295</v>
+        <v>0.3262</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3248</v>
+        <v>2.9986</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5037</v>
+        <v>2.6806</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5849</v>
+        <v>0.0824</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08119999999999999</v>
+        <v>2.5982</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1506</v>
+        <v>0.6443</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2554</v>
+        <v>0.2439</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.406</v>
+        <v>0.4004</v>
       </c>
       <c r="P6" t="n">
-        <v>0.194</v>
+        <v>-1.5523</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R6" t="n">
-        <v>0.194</v>
+        <v>0.3881</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8004</v>
+        <v>0.0174</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6068</v>
+        <v>0.1396</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1936</v>
+        <v>-0.1222</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.8358</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-2.1179</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. FUENTE DIEZ</t>
+          <t>M. ALONSO GONZÁLEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.355</v>
+        <v>-0.0543</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9618</v>
+        <v>-0.2368</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.3168</v>
+        <v>0.1825</v>
       </c>
       <c r="G7" t="n">
-        <v>3.3248</v>
+        <v>-0.6543</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3262</v>
+        <v>-0.3295</v>
       </c>
       <c r="I7" t="n">
-        <v>2.9986</v>
+        <v>-0.3248</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6806</v>
+        <v>-0.5037</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0824</v>
+        <v>-0.5849</v>
       </c>
       <c r="L7" t="n">
-        <v>2.5982</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6443</v>
+        <v>-0.1506</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2439</v>
+        <v>0.2554</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4004</v>
+        <v>-0.406</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.5523</v>
+        <v>0.194</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3881</v>
+        <v>0.194</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2918</v>
+        <v>0.406</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0606</v>
+        <v>0.2669</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2313</v>
+        <v>0.1391</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.8358</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.1179</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. GARCIA LARRACHE SEGURA</t>
+          <t>E. PASCUAL COZAR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7837</v>
+        <v>-0.2273</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.5685</v>
+        <v>1.0394</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7848</v>
+        <v>-1.2667</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8401999999999999</v>
+        <v>0.6489</v>
       </c>
       <c r="H8" t="n">
-        <v>1.8084</v>
+        <v>1.3157</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9681999999999999</v>
+        <v>-0.6667999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3766</v>
+        <v>1.3182</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8362000000000001</v>
+        <v>1.7013</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2129</v>
+        <v>-0.3832</v>
       </c>
       <c r="M8" t="n">
-        <v>1.2168</v>
+        <v>-0.6692</v>
       </c>
       <c r="N8" t="n">
-        <v>0.9721</v>
+        <v>-0.3856</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2447</v>
+        <v>-0.2836</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3881</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9105</v>
+        <v>-1.9403</v>
       </c>
       <c r="R8" t="n">
-        <v>2.5224</v>
+        <v>1.3582</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9538</v>
+        <v>-0.5762</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7874</v>
+        <v>0.1556</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1664</v>
+        <v>-0.7318</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2821</v>
+        <v>0.2821</v>
       </c>
       <c r="W8" t="n">
         <v>1.506</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.788</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. PASCUAL COZAR</t>
+          <t>L. GARCIA LARRACHE SEGURA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2944</v>
+        <v>-0.7137</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2176</v>
+        <v>-2.3078</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.512</v>
+        <v>1.594</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6489</v>
+        <v>0.8401999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>1.3157</v>
+        <v>1.8084</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6667999999999999</v>
+        <v>-0.9681999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3182</v>
+        <v>-0.3766</v>
       </c>
       <c r="K9" t="n">
-        <v>1.7013</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.3832</v>
+        <v>-1.2129</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6692</v>
+        <v>1.2168</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3856</v>
+        <v>0.9721</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2836</v>
+        <v>0.2447</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.5821</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9403</v>
+        <v>-2.9105</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3582</v>
+        <v>2.5224</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.6433</v>
+        <v>-0.8838</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6662</v>
+        <v>-0.5266</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9771</v>
+        <v>-0.3572</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2821</v>
+        <v>-0.2821</v>
       </c>
       <c r="W9" t="n">
         <v>1.506</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2239</v>
+        <v>-1.788</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.694</v>
+        <v>-2.2242</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4785</v>
+        <v>-1.1176</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2156</v>
+        <v>-1.1065</v>
       </c>
       <c r="G10" t="n">
         <v>0.1254</v>
@@ -1234,13 +1234,13 @@
         <v>1.1642</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2373</v>
+        <v>-0.7674</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6057</v>
+        <v>-0.2448</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6317</v>
+        <v>-0.5226</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6119</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.5157</v>
+        <v>-6.4519</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.1501</v>
+        <v>-5.8683</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3656</v>
+        <v>-0.5836</v>
       </c>
       <c r="G11" t="n">
         <v>-3.8609</v>
@@ -1312,13 +1312,13 @@
         <v>3.1045</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1772</v>
+        <v>-1.1134</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3017</v>
+        <v>-0.0199</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8754999999999999</v>
+        <v>-1.0935</v>
       </c>
       <c r="V11" t="n">
         <v>-2.4477</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>15.9093</v>
+        <v>16.8177</v>
       </c>
       <c r="E12" t="n">
-        <v>11.9333</v>
+        <v>12.8418</v>
       </c>
       <c r="F12" t="n">
-        <v>3.975899999999999</v>
+        <v>3.9759</v>
       </c>
       <c r="G12" t="n">
         <v>21.6112</v>
@@ -1390,13 +1390,13 @@
         <v>19.4032</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.949800000000001</v>
+        <v>-5.0412</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3535000000000002</v>
+        <v>0.5549000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-5.5964</v>
+        <v>-5.596399999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-1.6925</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.4785</v>
+        <v>3.6787</v>
       </c>
       <c r="E13" t="n">
-        <v>3.8169</v>
+        <v>4.0171</v>
       </c>
       <c r="F13" t="n">
         <v>-0.3385</v>
@@ -1468,10 +1468,10 @@
         <v>1.3582</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5339</v>
+        <v>0.7341</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7413</v>
+        <v>0.9415</v>
       </c>
       <c r="U13" t="n">
         <v>-0.2075</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1156</v>
+        <v>1.3431</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6352</v>
+        <v>1.8354</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5196</v>
+        <v>-0.4923</v>
       </c>
       <c r="G14" t="n">
         <v>0.9847</v>
@@ -1546,13 +1546,13 @@
         <v>0.7761</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9273</v>
+        <v>-0.6999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6057</v>
+        <v>-0.4055</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3217</v>
+        <v>-0.2944</v>
       </c>
       <c r="V14" t="n">
         <v>0.2821</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. CRESPO MONTESINOS</t>
+          <t>A. ROLDAN DE LA PORTILLA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2779</v>
+        <v>0.3692</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.3143</v>
+        <v>1.4381</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5921999999999999</v>
+        <v>-1.0689</v>
       </c>
       <c r="G15" t="n">
-        <v>-6.4226</v>
+        <v>0.0297</v>
       </c>
       <c r="H15" t="n">
-        <v>-6.1963</v>
+        <v>-0.2373</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2263</v>
+        <v>0.2669</v>
       </c>
       <c r="J15" t="n">
-        <v>-4.1786</v>
+        <v>0.0412</v>
       </c>
       <c r="K15" t="n">
-        <v>-4.247</v>
+        <v>0.0412</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0684</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.2441</v>
+        <v>-0.0115</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.9493</v>
+        <v>-0.2785</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2948</v>
+        <v>0.2669</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.194</v>
+        <v>0.194</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.3284</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1344</v>
+        <v>0.194</v>
       </c>
       <c r="S15" t="n">
-        <v>4.2393</v>
+        <v>0.1455</v>
       </c>
       <c r="T15" t="n">
-        <v>3.1807</v>
+        <v>0.173</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0586</v>
+        <v>-0.0275</v>
       </c>
       <c r="V15" t="n">
-        <v>2.6552</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>3.0119</v>
+        <v>1.2239</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.3567</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. ROLDAN DE LA PORTILLA</t>
+          <t>A. GARCIA QUILEZ CUERVAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2419</v>
+        <v>0.1862</v>
       </c>
       <c r="E16" t="n">
-        <v>1.338</v>
+        <v>0.0982</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0961</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0297</v>
+        <v>0.3074</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2373</v>
+        <v>-1.0389</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2669</v>
+        <v>1.3463</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0412</v>
+        <v>1.3946</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0412</v>
+        <v>0.7044</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>0.6901</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0115</v>
+        <v>-1.0871</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2785</v>
+        <v>-1.7433</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2669</v>
+        <v>0.6562</v>
       </c>
       <c r="P16" t="n">
-        <v>0.194</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-3.1045</v>
       </c>
       <c r="R16" t="n">
-        <v>0.194</v>
+        <v>2.7164</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0182</v>
+        <v>0.3892</v>
       </c>
       <c r="T16" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.5843</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0547</v>
+        <v>-0.1951</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.1224</v>
       </c>
       <c r="W16" t="n">
         <v>1.2239</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2239</v>
+        <v>-1.3463</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. GARCIA QUILEZ CUERVAS</t>
+          <t>D. MARINEZ FERNANDEZ-URRUTIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0771</v>
+        <v>-0.7585</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0982</v>
+        <v>-0.9006</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0211</v>
+        <v>0.142</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3074</v>
+        <v>-1.8899</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.0389</v>
+        <v>-1.0719</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3463</v>
+        <v>-0.8179999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3946</v>
+        <v>-1.2266</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7044</v>
+        <v>-0.5643</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6901</v>
+        <v>-0.6623</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0871</v>
+        <v>-0.6633</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.7433</v>
+        <v>-0.5075</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6562</v>
+        <v>-0.1557</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3881</v>
+        <v>1.1642</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.1045</v>
+        <v>-0.194</v>
       </c>
       <c r="R17" t="n">
-        <v>2.7164</v>
+        <v>1.3582</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2801</v>
+        <v>0.2493</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5843</v>
+        <v>0.5201</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3042</v>
+        <v>-0.2708</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1224</v>
+        <v>-0.2821</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.3463</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. MARINEZ FERNANDEZ-URRUTIA</t>
+          <t>O. HADI ADEGBITE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9036999999999999</v>
+        <v>-1.8344</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8005</v>
+        <v>0.1455</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1033</v>
+        <v>-1.9799</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.8899</v>
+        <v>-2.0716</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0719</v>
+        <v>-0.6163</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8179999999999999</v>
+        <v>-1.4554</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.2266</v>
+        <v>0.7327</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5643</v>
+        <v>0.6921</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6623</v>
+        <v>0.0406</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6633</v>
+        <v>-2.8043</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5075</v>
+        <v>-1.3083</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1557</v>
+        <v>-1.496</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1642</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.194</v>
+        <v>-1.1642</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3582</v>
+        <v>0.5821</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1041</v>
+        <v>0.8193</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6202</v>
+        <v>0.577</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5161</v>
+        <v>0.2423</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. HADI ADEGBITE</t>
+          <t>C. CRESPO MONTESINOS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3429</v>
+        <v>-1.8961</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7461</v>
+        <v>-1.9159</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.0889</v>
+        <v>0.0198</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.0716</v>
+        <v>-6.4226</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6163</v>
+        <v>-6.1963</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.4554</v>
+        <v>-0.2263</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7327</v>
+        <v>-4.1786</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6921</v>
+        <v>-4.247</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0406</v>
+        <v>0.0684</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.8043</v>
+        <v>-2.2441</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3083</v>
+        <v>-1.9493</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.496</v>
+        <v>-0.2948</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.5821</v>
+        <v>-0.194</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1642</v>
+        <v>-2.3284</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5821</v>
+        <v>2.1344</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3109</v>
+        <v>2.0654</v>
       </c>
       <c r="T19" t="n">
-        <v>1.1776</v>
+        <v>1.5791</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1332</v>
+        <v>0.4862</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>2.6552</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>3.0119</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.3567</v>
       </c>
     </row>
     <row r="20">
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0813</v>
+        <v>-2.2815</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1005</v>
+        <v>-0.3007</v>
       </c>
       <c r="F20" t="n">
         <v>-1.9808</v>
@@ -2014,10 +2014,10 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2793</v>
+        <v>0.0791</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5462</v>
+        <v>0.346</v>
       </c>
       <c r="U20" t="n">
         <v>-0.2669</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2445</v>
+        <v>-2.3624</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9151</v>
+        <v>-2.815</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6706</v>
+        <v>0.4526</v>
       </c>
       <c r="G21" t="n">
         <v>-5.402</v>
@@ -2092,13 +2092,13 @@
         <v>2.7164</v>
       </c>
       <c r="S21" t="n">
-        <v>1.177</v>
+        <v>1.059</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4508</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7261</v>
+        <v>0.5081</v>
       </c>
       <c r="V21" t="n">
         <v>0.2343</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4444</v>
+        <v>-2.4256</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3134</v>
+        <v>-0.5125999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.131</v>
+        <v>-1.913</v>
       </c>
       <c r="G22" t="n">
         <v>-1.8561</v>
@@ -2170,13 +2170,13 @@
         <v>1.3582</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.448</v>
+        <v>0.5709</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.387</v>
+        <v>0.4138</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.061</v>
+        <v>0.157</v>
       </c>
       <c r="V22" t="n">
         <v>-0.1702</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.7118</v>
+        <v>-3.2024</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6199</v>
+        <v>-1.2195</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0919</v>
+        <v>-1.9828</v>
       </c>
       <c r="G23" t="n">
         <v>0.2272</v>
@@ -2248,13 +2248,13 @@
         <v>2.3284</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1449</v>
+        <v>0.3645</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1436</v>
+        <v>0.2568</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0013</v>
+        <v>0.1077</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2716</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.3715</v>
+        <v>-6.7253</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.5466</v>
+        <v>-3.8459</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.8249</v>
+        <v>-2.8794</v>
       </c>
       <c r="G24" t="n">
         <v>-3.2243</v>
@@ -2326,13 +2326,13 @@
         <v>1.9403</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4726</v>
+        <v>0.1735</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0.0591</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1689</v>
+        <v>0.1144</v>
       </c>
       <c r="V24" t="n">
         <v>-1.3463</v>
@@ -2359,7 +2359,7 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-15.9091</v>
+        <v>-15.909</v>
       </c>
       <c r="E25" t="n">
         <v>-3.9759</v>
@@ -2395,7 +2395,7 @@
         <v>-5.589300000000001</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.940400000000001</v>
+        <v>-1.9404</v>
       </c>
       <c r="Q25" t="n">
         <v>-19.4032</v>
@@ -2404,13 +2404,13 @@
         <v>17.4627</v>
       </c>
       <c r="S25" t="n">
-        <v>5.949999999999999</v>
+        <v>5.9499</v>
       </c>
       <c r="T25" t="n">
-        <v>5.5961</v>
+        <v>5.596100000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3533999999999999</v>
+        <v>0.3534999999999999</v>
       </c>
       <c r="V25" t="n">
         <v>1.692399999999999</v>
